--- a/PSCBOX_S14.xlsx
+++ b/PSCBOX_S14.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N117"/>
+  <dimension ref="A1:N115"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -426,93 +426,84 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t># section : 평창~정선 도로건설공사 (3공구) / 일반 단면 제원도 / 8-018 / S=1:50 / 2007.12</t>
+          <t># page    : bim_pscbox_test.js  (S14 는 격벽이 아니다 — 일반 박스 단면)</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t># rebar   : 주두부 배근도(1) / 8-243 / S=1:30   -- SECTION A-A 가 S14 다 (깊이 6,853 일치)</t>
+          <t># section : 평창~정선 도로건설공사 (3공구) / 일반 단면 제원도 / 8-018 / S=1:50 / 2007.12</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t># duct    : 강연선 배치 단면 (TC1 TC2 + 3..21 / 4..20 / TS1 TS2)</t>
+          <t># rebar   : 주두부 배근도(1) / 8-243 / S=1:30   -- SECTION A-A 가 S14 다 (깊이 6,853 일치)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>#</t>
+          <t># duct    : 강연선 배치 단면 (TC1 TC2 + 3..21 / 4..20 / TS1 TS2)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t># 8-018 단면 제원표 :  S14   Y1 = 6,853   Y2 = 743   Y3 = 6,110   AREA = 16.061 m2</t>
+          <t>#</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>#   Y1 전체 높이(중심선) · Y2 바닥슬래브 두께 · Y3 = Y1 - Y2</t>
+          <t># 8-018 단면 제원표 :  S14   Y1 = 6,853   Y2 = 743   Y3 = 6,110   AREA = 16.061 m2</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>#   덕트 그림의 280 + 5,830 + 743 = 6,853 과 정확히 맞는다</t>
+          <t>#   Y1 전체 높이(중심선) · Y2 바닥슬래브 두께 · Y3 = Y1 - Y2</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>type</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>1c</t>
+          <t>#   덕트 그림의 280 + 5,830 + 743 = 6,853 과 정확히 맞는다</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>seg</t>
-        </is>
-      </c>
-      <c r="B10" t="n">
-        <v>4750</v>
-      </c>
-      <c r="C10" t="inlineStr"/>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>8-018 : 12 @ 4,750 = 57,000</t>
+          <t>type</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>1c</t>
         </is>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>dia</t>
+          <t>seg</t>
         </is>
       </c>
       <c r="B11" t="n">
-        <v>2000</v>
+        <v>4750</v>
       </c>
       <c r="C11" t="inlineStr"/>
       <c r="D11" t="inlineStr">
         <is>
-          <t>S14 에는 격벽이 없다 — crebar 를 쓸 때만 의미가 있다</t>
+          <t>8-018 : 12 @ 4,750 = 57,000</t>
         </is>
       </c>
     </row>
@@ -1032,130 +1023,181 @@
       </c>
     </row>
     <row r="47">
-      <c r="A47" t="inlineStr">
-        <is>
-          <t># ---- S14 has no diaphragm ----</t>
-        </is>
-      </c>
+      <c r="A47" t="inlineStr"/>
     </row>
     <row r="48">
       <c r="A48" t="inlineStr">
         <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="B48" t="inlineStr">
-        <is>
-          <t>none</t>
+          <t># ================= DUCT =================================================</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" t="inlineStr"/>
+      <c r="A49" t="inlineStr">
+        <is>
+          <t># duct | id | shape | D | H | x | y | ref | clr        (문법은 bim_duct.js)</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="inlineStr">
         <is>
-          <t># ================= DUCT =================================================</t>
+          <t>#   shape  circ = D 가 외경 · rect = D 폭, H 높이</t>
         </is>
       </c>
     </row>
     <row r="51">
       <c r="A51" t="inlineStr">
         <is>
-          <t># duct | id | shape | D | H | x | y | ref | clr</t>
+          <t>#   x      단면 좌표 (중심선 기준, 오른쪽 +)</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" t="inlineStr">
         <is>
-          <t>#   shape  circ = D 가 외경 · rect = D 폭, H 높이</t>
+          <t>#   y      ref 에서 잰 깊이.  ref = deck(상면에서 아래·기본) / soffit / abs</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="inlineStr">
         <is>
-          <t>#   x      단면 좌표 (중심선 기준, 오른쪽 +)</t>
+          <t>#          상면이 -3% 로 기울어 있으므로 같은 y 라도 x 에 따라 절대높이가 다르다</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="inlineStr">
         <is>
-          <t>#   y      ref 에서 잰 깊이.  ref = deck(상면에서 아래·기본) / soffit / abs</t>
+          <t>#   clr    철근과의 최소 순간격. 비우면 내측 피복(30)</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="inlineStr">
         <is>
-          <t>#          상면이 -3% 로 기울어 있으므로 같은 y 라도 x 에 따라 절대높이가 다르다</t>
+          <t>#</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="inlineStr">
         <is>
-          <t>#   clr    철근과의 최소 순간격. 비우면 내측 피복(30)</t>
+          <t># ! x 는 도면 치수체인에서 정확히 복원했다 :</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>#     1215+150+150+200+150+150+300+300+670+4+290+286+280+150+150+200+150+150+1255</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="inlineStr">
         <is>
-          <t># ! x 는 도면 치수체인에서 정확히 복원했다 :</t>
+          <t>#     = 6,200  (선단에서 중심선까지, 정확히 떨어진다)</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="inlineStr">
         <is>
-          <t>#     1215+150+150+200+150+150+300+300+670+4+290+286+280+150+150+200+150+150+1255</t>
+          <t># ! y(깊이)와 외경은 **덕트 그림을 픽셀로 잰 값**이다 (±10 mm).</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="inlineStr">
         <is>
-          <t>#     = 6,200  (선단에서 중심선까지, 정확히 떨어진다)</t>
+          <t>#     도면에 적힌 세로 치수 160 · 300 과는 맞는다. 원문 치수로 확인이 필요하다.</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="inlineStr">
         <is>
-          <t># ! y(깊이)와 외경은 **덕트 그림을 픽셀로 잰 값**이다 (±10 mm).</t>
+          <t># ! id 는 잠정이다 — 도면의 3..21 / 4..20 / TS1 TS2 배정은 확인이 필요하다.</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="inlineStr">
         <is>
-          <t>#     도면에 적힌 세로 치수 160 · 300 과는 맞는다. 원문 치수로 확인이 필요하다.</t>
+          <t># --- 상단 열 : 상면에서 160 ---</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="inlineStr">
         <is>
-          <t># ! id 는 잠정이다 — 도면의 3..21 / 4..20 / TS1 TS2 배정은 확인이 필요하다.</t>
-        </is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>AL1</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>120</v>
+      </c>
+      <c r="E63" t="inlineStr"/>
+      <c r="F63" t="n">
+        <v>-1555</v>
+      </c>
+      <c r="G63" t="n">
+        <v>160</v>
+      </c>
+      <c r="H63" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I63" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="inlineStr">
         <is>
-          <t># --- 상단 열 : 상면에서 160 ---</t>
-        </is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>AL2</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>120</v>
+      </c>
+      <c r="E64" t="inlineStr"/>
+      <c r="F64" t="n">
+        <v>-1905</v>
+      </c>
+      <c r="G64" t="n">
+        <v>160</v>
+      </c>
+      <c r="H64" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I64" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="65">
@@ -1166,7 +1208,7 @@
       </c>
       <c r="B65" t="inlineStr">
         <is>
-          <t>AL1</t>
+          <t>AL3</t>
         </is>
       </c>
       <c r="C65" t="inlineStr">
@@ -1179,7 +1221,7 @@
       </c>
       <c r="E65" t="inlineStr"/>
       <c r="F65" t="n">
-        <v>-1555</v>
+        <v>-2055</v>
       </c>
       <c r="G65" t="n">
         <v>160</v>
@@ -1201,7 +1243,7 @@
       </c>
       <c r="B66" t="inlineStr">
         <is>
-          <t>AL2</t>
+          <t>AL4</t>
         </is>
       </c>
       <c r="C66" t="inlineStr">
@@ -1214,7 +1256,7 @@
       </c>
       <c r="E66" t="inlineStr"/>
       <c r="F66" t="n">
-        <v>-1905</v>
+        <v>-2335</v>
       </c>
       <c r="G66" t="n">
         <v>160</v>
@@ -1236,7 +1278,7 @@
       </c>
       <c r="B67" t="inlineStr">
         <is>
-          <t>AL3</t>
+          <t>AL5</t>
         </is>
       </c>
       <c r="C67" t="inlineStr">
@@ -1249,7 +1291,7 @@
       </c>
       <c r="E67" t="inlineStr"/>
       <c r="F67" t="n">
-        <v>-2055</v>
+        <v>-4185</v>
       </c>
       <c r="G67" t="n">
         <v>160</v>
@@ -1271,7 +1313,7 @@
       </c>
       <c r="B68" t="inlineStr">
         <is>
-          <t>AL4</t>
+          <t>AL6</t>
         </is>
       </c>
       <c r="C68" t="inlineStr">
@@ -1284,7 +1326,7 @@
       </c>
       <c r="E68" t="inlineStr"/>
       <c r="F68" t="n">
-        <v>-2335</v>
+        <v>-4335</v>
       </c>
       <c r="G68" t="n">
         <v>160</v>
@@ -1306,7 +1348,7 @@
       </c>
       <c r="B69" t="inlineStr">
         <is>
-          <t>AL5</t>
+          <t>AL7</t>
         </is>
       </c>
       <c r="C69" t="inlineStr">
@@ -1319,7 +1361,7 @@
       </c>
       <c r="E69" t="inlineStr"/>
       <c r="F69" t="n">
-        <v>-4185</v>
+        <v>-4485</v>
       </c>
       <c r="G69" t="n">
         <v>160</v>
@@ -1341,7 +1383,7 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>AL6</t>
+          <t>AL8</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
@@ -1354,7 +1396,7 @@
       </c>
       <c r="E70" t="inlineStr"/>
       <c r="F70" t="n">
-        <v>-4335</v>
+        <v>-4835</v>
       </c>
       <c r="G70" t="n">
         <v>160</v>
@@ -1376,7 +1418,7 @@
       </c>
       <c r="B71" t="inlineStr">
         <is>
-          <t>AL7</t>
+          <t>AR1</t>
         </is>
       </c>
       <c r="C71" t="inlineStr">
@@ -1389,7 +1431,7 @@
       </c>
       <c r="E71" t="inlineStr"/>
       <c r="F71" t="n">
-        <v>-4485</v>
+        <v>1555</v>
       </c>
       <c r="G71" t="n">
         <v>160</v>
@@ -1411,7 +1453,7 @@
       </c>
       <c r="B72" t="inlineStr">
         <is>
-          <t>AL8</t>
+          <t>AR2</t>
         </is>
       </c>
       <c r="C72" t="inlineStr">
@@ -1424,7 +1466,7 @@
       </c>
       <c r="E72" t="inlineStr"/>
       <c r="F72" t="n">
-        <v>-4835</v>
+        <v>1905</v>
       </c>
       <c r="G72" t="n">
         <v>160</v>
@@ -1446,7 +1488,7 @@
       </c>
       <c r="B73" t="inlineStr">
         <is>
-          <t>AR1</t>
+          <t>AR3</t>
         </is>
       </c>
       <c r="C73" t="inlineStr">
@@ -1459,7 +1501,7 @@
       </c>
       <c r="E73" t="inlineStr"/>
       <c r="F73" t="n">
-        <v>1555</v>
+        <v>2055</v>
       </c>
       <c r="G73" t="n">
         <v>160</v>
@@ -1481,7 +1523,7 @@
       </c>
       <c r="B74" t="inlineStr">
         <is>
-          <t>AR2</t>
+          <t>AR4</t>
         </is>
       </c>
       <c r="C74" t="inlineStr">
@@ -1494,7 +1536,7 @@
       </c>
       <c r="E74" t="inlineStr"/>
       <c r="F74" t="n">
-        <v>1905</v>
+        <v>2335</v>
       </c>
       <c r="G74" t="n">
         <v>160</v>
@@ -1516,7 +1558,7 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>AR3</t>
+          <t>AR5</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
@@ -1529,7 +1571,7 @@
       </c>
       <c r="E75" t="inlineStr"/>
       <c r="F75" t="n">
-        <v>2055</v>
+        <v>4185</v>
       </c>
       <c r="G75" t="n">
         <v>160</v>
@@ -1551,7 +1593,7 @@
       </c>
       <c r="B76" t="inlineStr">
         <is>
-          <t>AR4</t>
+          <t>AR6</t>
         </is>
       </c>
       <c r="C76" t="inlineStr">
@@ -1564,7 +1606,7 @@
       </c>
       <c r="E76" t="inlineStr"/>
       <c r="F76" t="n">
-        <v>2335</v>
+        <v>4335</v>
       </c>
       <c r="G76" t="n">
         <v>160</v>
@@ -1586,7 +1628,7 @@
       </c>
       <c r="B77" t="inlineStr">
         <is>
-          <t>AR5</t>
+          <t>AR7</t>
         </is>
       </c>
       <c r="C77" t="inlineStr">
@@ -1599,7 +1641,7 @@
       </c>
       <c r="E77" t="inlineStr"/>
       <c r="F77" t="n">
-        <v>4185</v>
+        <v>4485</v>
       </c>
       <c r="G77" t="n">
         <v>160</v>
@@ -1621,7 +1663,7 @@
       </c>
       <c r="B78" t="inlineStr">
         <is>
-          <t>AR6</t>
+          <t>AR8</t>
         </is>
       </c>
       <c r="C78" t="inlineStr">
@@ -1634,7 +1676,7 @@
       </c>
       <c r="E78" t="inlineStr"/>
       <c r="F78" t="n">
-        <v>4335</v>
+        <v>4835</v>
       </c>
       <c r="G78" t="n">
         <v>160</v>
@@ -1651,36 +1693,8 @@
     <row r="79">
       <c r="A79" t="inlineStr">
         <is>
-          <t>duct</t>
-        </is>
-      </c>
-      <c r="B79" t="inlineStr">
-        <is>
-          <t>AR7</t>
-        </is>
-      </c>
-      <c r="C79" t="inlineStr">
-        <is>
-          <t>circ</t>
-        </is>
-      </c>
-      <c r="D79" t="n">
-        <v>120</v>
-      </c>
-      <c r="E79" t="inlineStr"/>
-      <c r="F79" t="n">
-        <v>4485</v>
-      </c>
-      <c r="G79" t="n">
-        <v>160</v>
-      </c>
-      <c r="H79" t="inlineStr">
-        <is>
-          <t>deck</t>
-        </is>
-      </c>
-      <c r="I79" t="n">
-        <v>25</v>
+          <t># --- 하단 열 : 상면에서 310 ---</t>
+        </is>
       </c>
     </row>
     <row r="80">
@@ -1691,7 +1705,7 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>AR8</t>
+          <t>BL1</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
@@ -1704,10 +1718,10 @@
       </c>
       <c r="E80" t="inlineStr"/>
       <c r="F80" t="n">
-        <v>4835</v>
+        <v>-2335</v>
       </c>
       <c r="G80" t="n">
-        <v>160</v>
+        <v>310</v>
       </c>
       <c r="H80" t="inlineStr">
         <is>
@@ -1721,8 +1735,36 @@
     <row r="81">
       <c r="A81" t="inlineStr">
         <is>
-          <t># --- 하단 열 : 상면에서 310 ---</t>
-        </is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>BL2</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>120</v>
+      </c>
+      <c r="E81" t="inlineStr"/>
+      <c r="F81" t="n">
+        <v>-4335</v>
+      </c>
+      <c r="G81" t="n">
+        <v>310</v>
+      </c>
+      <c r="H81" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I81" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="82">
@@ -1733,7 +1775,7 @@
       </c>
       <c r="B82" t="inlineStr">
         <is>
-          <t>BL1</t>
+          <t>BR1</t>
         </is>
       </c>
       <c r="C82" t="inlineStr">
@@ -1746,7 +1788,7 @@
       </c>
       <c r="E82" t="inlineStr"/>
       <c r="F82" t="n">
-        <v>-2335</v>
+        <v>2335</v>
       </c>
       <c r="G82" t="n">
         <v>310</v>
@@ -1768,7 +1810,7 @@
       </c>
       <c r="B83" t="inlineStr">
         <is>
-          <t>BL2</t>
+          <t>BR2</t>
         </is>
       </c>
       <c r="C83" t="inlineStr">
@@ -1781,7 +1823,7 @@
       </c>
       <c r="E83" t="inlineStr"/>
       <c r="F83" t="n">
-        <v>-4335</v>
+        <v>4335</v>
       </c>
       <c r="G83" t="n">
         <v>310</v>
@@ -1798,36 +1840,8 @@
     <row r="84">
       <c r="A84" t="inlineStr">
         <is>
-          <t>duct</t>
-        </is>
-      </c>
-      <c r="B84" t="inlineStr">
-        <is>
-          <t>BR1</t>
-        </is>
-      </c>
-      <c r="C84" t="inlineStr">
-        <is>
-          <t>circ</t>
-        </is>
-      </c>
-      <c r="D84" t="n">
-        <v>120</v>
-      </c>
-      <c r="E84" t="inlineStr"/>
-      <c r="F84" t="n">
-        <v>2335</v>
-      </c>
-      <c r="G84" t="n">
-        <v>310</v>
-      </c>
-      <c r="H84" t="inlineStr">
-        <is>
-          <t>deck</t>
-        </is>
-      </c>
-      <c r="I84" t="n">
-        <v>25</v>
+          <t># --- 복부 쪽 무리 ---</t>
+        </is>
       </c>
     </row>
     <row r="85">
@@ -1838,7 +1852,7 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>BR2</t>
+          <t>WL1</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
@@ -1851,10 +1865,10 @@
       </c>
       <c r="E85" t="inlineStr"/>
       <c r="F85" t="n">
-        <v>4335</v>
+        <v>-2865</v>
       </c>
       <c r="G85" t="n">
-        <v>310</v>
+        <v>245</v>
       </c>
       <c r="H85" t="inlineStr">
         <is>
@@ -1868,8 +1882,36 @@
     <row r="86">
       <c r="A86" t="inlineStr">
         <is>
-          <t># --- 복부 쪽 무리 ---</t>
-        </is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>WL2</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>120</v>
+      </c>
+      <c r="E86" t="inlineStr"/>
+      <c r="F86" t="n">
+        <v>-3515</v>
+      </c>
+      <c r="G86" t="n">
+        <v>360</v>
+      </c>
+      <c r="H86" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I86" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="87">
@@ -1880,7 +1922,7 @@
       </c>
       <c r="B87" t="inlineStr">
         <is>
-          <t>WL1</t>
+          <t>WL3</t>
         </is>
       </c>
       <c r="C87" t="inlineStr">
@@ -1893,10 +1935,10 @@
       </c>
       <c r="E87" t="inlineStr"/>
       <c r="F87" t="n">
-        <v>-2865</v>
+        <v>-3715</v>
       </c>
       <c r="G87" t="n">
-        <v>245</v>
+        <v>425</v>
       </c>
       <c r="H87" t="inlineStr">
         <is>
@@ -1915,7 +1957,7 @@
       </c>
       <c r="B88" t="inlineStr">
         <is>
-          <t>WL2</t>
+          <t>WR1</t>
         </is>
       </c>
       <c r="C88" t="inlineStr">
@@ -1928,10 +1970,10 @@
       </c>
       <c r="E88" t="inlineStr"/>
       <c r="F88" t="n">
-        <v>-3515</v>
+        <v>2865</v>
       </c>
       <c r="G88" t="n">
-        <v>360</v>
+        <v>245</v>
       </c>
       <c r="H88" t="inlineStr">
         <is>
@@ -1950,7 +1992,7 @@
       </c>
       <c r="B89" t="inlineStr">
         <is>
-          <t>WL3</t>
+          <t>WR2</t>
         </is>
       </c>
       <c r="C89" t="inlineStr">
@@ -1963,10 +2005,10 @@
       </c>
       <c r="E89" t="inlineStr"/>
       <c r="F89" t="n">
-        <v>-3715</v>
+        <v>3515</v>
       </c>
       <c r="G89" t="n">
-        <v>425</v>
+        <v>360</v>
       </c>
       <c r="H89" t="inlineStr">
         <is>
@@ -1985,7 +2027,7 @@
       </c>
       <c r="B90" t="inlineStr">
         <is>
-          <t>WR1</t>
+          <t>WR3</t>
         </is>
       </c>
       <c r="C90" t="inlineStr">
@@ -1998,10 +2040,10 @@
       </c>
       <c r="E90" t="inlineStr"/>
       <c r="F90" t="n">
-        <v>2865</v>
+        <v>3715</v>
       </c>
       <c r="G90" t="n">
-        <v>245</v>
+        <v>425</v>
       </c>
       <c r="H90" t="inlineStr">
         <is>
@@ -2015,36 +2057,8 @@
     <row r="91">
       <c r="A91" t="inlineStr">
         <is>
-          <t>duct</t>
-        </is>
-      </c>
-      <c r="B91" t="inlineStr">
-        <is>
-          <t>WR2</t>
-        </is>
-      </c>
-      <c r="C91" t="inlineStr">
-        <is>
-          <t>circ</t>
-        </is>
-      </c>
-      <c r="D91" t="n">
-        <v>120</v>
-      </c>
-      <c r="E91" t="inlineStr"/>
-      <c r="F91" t="n">
-        <v>3515</v>
-      </c>
-      <c r="G91" t="n">
-        <v>360</v>
-      </c>
-      <c r="H91" t="inlineStr">
-        <is>
-          <t>deck</t>
-        </is>
-      </c>
-      <c r="I91" t="n">
-        <v>25</v>
+          <t># --- TC1 TC2 : 큰 덕트 ---</t>
+        </is>
       </c>
     </row>
     <row r="92">
@@ -2055,7 +2069,7 @@
       </c>
       <c r="B92" t="inlineStr">
         <is>
-          <t>WR3</t>
+          <t>TC1L</t>
         </is>
       </c>
       <c r="C92" t="inlineStr">
@@ -2064,14 +2078,14 @@
         </is>
       </c>
       <c r="D92" t="n">
-        <v>120</v>
+        <v>440</v>
       </c>
       <c r="E92" t="inlineStr"/>
       <c r="F92" t="n">
-        <v>3715</v>
+        <v>-2766</v>
       </c>
       <c r="G92" t="n">
-        <v>425</v>
+        <v>300</v>
       </c>
       <c r="H92" t="inlineStr">
         <is>
@@ -2085,8 +2099,36 @@
     <row r="93">
       <c r="A93" t="inlineStr">
         <is>
-          <t># --- TC1 TC2 : 큰 덕트 ---</t>
-        </is>
+          <t>duct</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>TC2L</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>circ</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>440</v>
+      </c>
+      <c r="E93" t="inlineStr"/>
+      <c r="F93" t="n">
+        <v>-3585</v>
+      </c>
+      <c r="G93" t="n">
+        <v>300</v>
+      </c>
+      <c r="H93" t="inlineStr">
+        <is>
+          <t>deck</t>
+        </is>
+      </c>
+      <c r="I93" t="n">
+        <v>25</v>
       </c>
     </row>
     <row r="94">
@@ -2097,7 +2139,7 @@
       </c>
       <c r="B94" t="inlineStr">
         <is>
-          <t>TC1L</t>
+          <t>TC1R</t>
         </is>
       </c>
       <c r="C94" t="inlineStr">
@@ -2110,7 +2152,7 @@
       </c>
       <c r="E94" t="inlineStr"/>
       <c r="F94" t="n">
-        <v>-2766</v>
+        <v>2766</v>
       </c>
       <c r="G94" t="n">
         <v>300</v>
@@ -2132,7 +2174,7 @@
       </c>
       <c r="B95" t="inlineStr">
         <is>
-          <t>TC2L</t>
+          <t>TC2R</t>
         </is>
       </c>
       <c r="C95" t="inlineStr">
@@ -2145,7 +2187,7 @@
       </c>
       <c r="E95" t="inlineStr"/>
       <c r="F95" t="n">
-        <v>-3585</v>
+        <v>3585</v>
       </c>
       <c r="G95" t="n">
         <v>300</v>
@@ -2160,117 +2202,139 @@
       </c>
     </row>
     <row r="96">
-      <c r="A96" t="inlineStr">
-        <is>
-          <t>duct</t>
-        </is>
-      </c>
-      <c r="B96" t="inlineStr">
-        <is>
-          <t>TC1R</t>
-        </is>
-      </c>
-      <c r="C96" t="inlineStr">
-        <is>
-          <t>circ</t>
-        </is>
-      </c>
-      <c r="D96" t="n">
-        <v>440</v>
-      </c>
-      <c r="E96" t="inlineStr"/>
-      <c r="F96" t="n">
-        <v>2766</v>
-      </c>
-      <c r="G96" t="n">
-        <v>300</v>
-      </c>
-      <c r="H96" t="inlineStr">
-        <is>
-          <t>deck</t>
-        </is>
-      </c>
-      <c r="I96" t="n">
-        <v>25</v>
-      </c>
+      <c r="A96" t="inlineStr"/>
     </row>
     <row r="97">
       <c r="A97" t="inlineStr">
         <is>
-          <t>duct</t>
-        </is>
-      </c>
-      <c r="B97" t="inlineStr">
-        <is>
-          <t>TC2R</t>
-        </is>
-      </c>
-      <c r="C97" t="inlineStr">
-        <is>
-          <t>circ</t>
-        </is>
-      </c>
-      <c r="D97" t="n">
-        <v>440</v>
-      </c>
-      <c r="E97" t="inlineStr"/>
-      <c r="F97" t="n">
-        <v>3585</v>
-      </c>
-      <c r="G97" t="n">
-        <v>300</v>
-      </c>
-      <c r="H97" t="inlineStr">
-        <is>
-          <t>deck</t>
-        </is>
-      </c>
-      <c r="I97" t="n">
-        <v>25</v>
+          <t># ================= REBAR ================================================</t>
+        </is>
       </c>
     </row>
     <row r="98">
-      <c r="A98" t="inlineStr"/>
+      <c r="A98" t="inlineStr">
+        <is>
+          <t># 8-243 SECTION A-A (= S14). 먼저 S15 에서 도는 것과 같은 꼴만 넣었다.</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="inlineStr">
         <is>
-          <t># ================= REBAR ================================================</t>
+          <t># trebar | id | code | dia | init x,y,rot | set | segs | angs | nors | end:start | end:end | radius | z</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t># 8-243 SECTION A-A (= S14). 먼저 S15 에서 도는 것과 같은 꼴만 넣었다.</t>
+          <t>#   code 1 = 직선(A) · 11 = ㄱ자(A-&gt;B). angs 의 a 는 A 다음 꺾임각</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t># trebar | id | code | dia | init x,y,rot | set | segs | angs | nors | end:start | end:end | radius | z</t>
+          <t>#   꺾임각 88.282 / 91.718 = 데크 -3% 에 대해 다리가 연직 (90 -+ 1.718)</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>#   code 1 = 직선(A) · 11 = ㄱ자(A-&gt;B). angs 의 a 는 A 다음 꺾임각</t>
+          <t>#   다리 190 = 선단두께 280 - 2 x 피복 45  (8-244 에서 확인한 유도값)</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>#   꺾임각 88.282 / 91.718 = 데크 -3% 에 대해 다리가 연직 (90 -+ 1.718)</t>
+          <t>trebar</t>
+        </is>
+      </c>
+      <c r="B103" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="C103" t="n">
+        <v>11</v>
+      </c>
+      <c r="D103" t="n">
+        <v>13</v>
+      </c>
+      <c r="E103" t="inlineStr"/>
+      <c r="F103" t="inlineStr">
+        <is>
+          <t>b:E1</t>
+        </is>
+      </c>
+      <c r="G103" t="inlineStr">
+        <is>
+          <t>a:190,b:4800</t>
+        </is>
+      </c>
+      <c r="H103" t="inlineStr">
+        <is>
+          <t>a:88.282</t>
+        </is>
+      </c>
+      <c r="I103" t="inlineStr"/>
+      <c r="J103" t="inlineStr"/>
+      <c r="K103" t="inlineStr"/>
+      <c r="L103" t="inlineStr"/>
+      <c r="M103" t="n">
+        <v>0</v>
+      </c>
+      <c r="N103" t="inlineStr">
+        <is>
+          <t>deck top, left  : 190 + 4,500 + 300 lap = 4,990  (8-243 (1)-1 N=110)</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>#   다리 190 = 선단두께 280 - 2 x 피복 45  (8-244 에서 확인한 유도값)</t>
+          <t>trebar</t>
+        </is>
+      </c>
+      <c r="B104" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C104" t="n">
+        <v>11</v>
+      </c>
+      <c r="D104" t="n">
+        <v>13</v>
+      </c>
+      <c r="E104" t="inlineStr"/>
+      <c r="F104" t="inlineStr">
+        <is>
+          <t>a:E2</t>
+        </is>
+      </c>
+      <c r="G104" t="inlineStr">
+        <is>
+          <t>a:7810,b:190</t>
+        </is>
+      </c>
+      <c r="H104" t="inlineStr">
+        <is>
+          <t>a:91.718</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
+      <c r="J104" t="inlineStr"/>
+      <c r="K104" t="inlineStr"/>
+      <c r="L104" t="inlineStr"/>
+      <c r="M104" t="n">
+        <v>0</v>
+      </c>
+      <c r="N104" t="inlineStr">
+        <is>
+          <t>deck top, right : 300 lap + 7,510 + 190 = 8,000  (8-243 (1) N=110)</t>
         </is>
       </c>
     </row>
@@ -2282,7 +2346,7 @@
       </c>
       <c r="B105" t="inlineStr">
         <is>
-          <t>1-1</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C105" t="n">
@@ -2294,12 +2358,12 @@
       <c r="E105" t="inlineStr"/>
       <c r="F105" t="inlineStr">
         <is>
-          <t>b:E1</t>
+          <t>b:E4</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>a:190,b:4800</t>
+          <t>a:190,b:1400</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
@@ -2316,167 +2380,75 @@
       </c>
       <c r="N105" t="inlineStr">
         <is>
-          <t>deck top, left  : 190 + 4,500 + 300 lap = 4,990  (8-243 (1)-1 N=110)</t>
+          <t>right cantilever soffit at the tip = 1,590  (8-243 (2) N=110)</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>trebar</t>
-        </is>
-      </c>
-      <c r="B106" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C106" t="n">
-        <v>11</v>
-      </c>
-      <c r="D106" t="n">
-        <v>13</v>
-      </c>
-      <c r="E106" t="inlineStr"/>
-      <c r="F106" t="inlineStr">
-        <is>
-          <t>a:E2</t>
-        </is>
-      </c>
-      <c r="G106" t="inlineStr">
-        <is>
-          <t>a:7810,b:190</t>
-        </is>
-      </c>
-      <c r="H106" t="inlineStr">
-        <is>
-          <t>a:91.718</t>
-        </is>
-      </c>
-      <c r="I106" t="inlineStr"/>
-      <c r="J106" t="inlineStr"/>
-      <c r="K106" t="inlineStr"/>
-      <c r="L106" t="inlineStr"/>
-      <c r="M106" t="n">
-        <v>0</v>
-      </c>
-      <c r="N106" t="inlineStr">
-        <is>
-          <t>deck top, right : 300 lap + 7,510 + 190 = 8,000  (8-243 (1) N=110)</t>
+          <t># trebar | 2-1 | 11 | 13 | | b:E13 | a:190,b:1400 | a:-91.718 | | | | | 0 | off: the left wall runs the other way. Needs growing against the wall direction</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>trebar</t>
-        </is>
-      </c>
-      <c r="B107" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C107" t="n">
-        <v>11</v>
-      </c>
-      <c r="D107" t="n">
-        <v>13</v>
-      </c>
-      <c r="E107" t="inlineStr"/>
-      <c r="F107" t="inlineStr">
-        <is>
-          <t>b:E4</t>
-        </is>
-      </c>
-      <c r="G107" t="inlineStr">
-        <is>
-          <t>a:190,b:1400</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr">
-        <is>
-          <t>a:88.282</t>
-        </is>
-      </c>
-      <c r="I107" t="inlineStr"/>
-      <c r="J107" t="inlineStr"/>
-      <c r="K107" t="inlineStr"/>
-      <c r="L107" t="inlineStr"/>
-      <c r="M107" t="n">
-        <v>0</v>
-      </c>
-      <c r="N107" t="inlineStr">
-        <is>
-          <t>right cantilever soffit at the tip = 1,590  (8-243 (2) N=110)</t>
+          <t>#</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t># trebar | 2-1 | 11 | 13 | | b:E13 | a:190,b:1400 | a:-91.718 | | | | | 0 | off: the left wall runs the other way. Needs growing against the wall direction</t>
+          <t># --- 아직 안 넣은 것 (8-243 에 있다. 배치면을 정해야 한다) ---</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>#   (3)  H13 L=5,055 N=110      (4)  H13 L=5,035 N=110      (5) H13 L=4,000 N=110</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t># --- 아직 안 넣은 것 (8-243 에 있다. 배치면을 정해야 한다) ---</t>
+          <t>#   (6)-1~(6)-4  H22  A.v.r L=8,257  N=110   본체 6,763~7,710  + 다리 510 x 2</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>#   (3)  H13 L=5,055 N=110      (4)  H13 L=5,035 N=110      (5) H13 L=4,000 N=110</t>
+          <t>#       -&gt; (6,763+7,710)/2 + 1,020 = 8,257 로 정확히 맞는다. **길이가 출력인 사례**</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>#   (6)-1~(6)-4  H22  A.v.r L=8,257  N=110   본체 6,763~7,710  + 다리 510 x 2</t>
+          <t>#   (7)(7a) L=4,000  (8)(8a) L=3,090  (9)(9a) L=1,890/1,960  (10) H19 L=6,000</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>#       -&gt; (6,763+7,710)/2 + 1,020 = 8,257 로 정확히 맞는다. **길이가 출력인 사례**</t>
+          <t>#   (11)(11-1)(12) H13  ㄷ자 500 x 150,  X = 206~480 / 212~486 (범위!)</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>#   (7)(7a) L=4,000  (8)(8a) L=3,090  (9)(9a) L=1,890/1,960  (10) H19 L=6,000</t>
+          <t>#   T2 H13 L=700 N=520 · T3 · D1 H16 · D2 H13 · D3 H16 · S2 H13</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
-        <is>
-          <t>#   (11)(11-1)(12) H13  ㄷ자 500 x 150,  X = 206~480 / 212~486 (범위!)</t>
-        </is>
-      </c>
-    </row>
-    <row r="116">
-      <c r="A116" t="inlineStr">
-        <is>
-          <t>#   T2 H13 L=700 N=520 · T3 · D1 H16 · D2 H13 · D3 H16 · S2 H13</t>
-        </is>
-      </c>
-    </row>
-    <row r="117">
-      <c r="A117" t="inlineStr">
         <is>
           <t>end</t>
         </is>

--- a/PSCBOX_S14.xlsx
+++ b/PSCBOX_S14.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N115"/>
+  <dimension ref="A1:N126"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2228,227 +2228,292 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>#   code 1 = 직선(A) · 11 = ㄱ자(A-&gt;B). angs 의 a 는 A 다음 꺾임각</t>
+          <t>#   code 11 = ㄱ자(A-&gt;B).  세그먼트는 **다리(190) 먼저**, 그 다음 몸통.</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>#   꺾임각 88.282 / 91.718 = 데크 -3% 에 대해 다리가 연직 (90 -+ 1.718)</t>
+          <t>#</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t>#   다리 190 = 선단두께 280 - 2 x 피복 45  (8-244 에서 확인한 유도값)</t>
+          <t># 입력에서 뺀 것 — 엔진이 스스로 찾는다 :</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>trebar</t>
-        </is>
-      </c>
-      <c r="B103" t="inlineStr">
-        <is>
-          <t>1-1</t>
-        </is>
-      </c>
-      <c r="C103" t="n">
-        <v>11</v>
-      </c>
-      <c r="D103" t="n">
-        <v>13</v>
-      </c>
-      <c r="E103" t="inlineStr"/>
-      <c r="F103" t="inlineStr">
-        <is>
-          <t>b:E1</t>
-        </is>
-      </c>
-      <c r="G103" t="inlineStr">
-        <is>
-          <t>a:190,b:4800</t>
-        </is>
-      </c>
-      <c r="H103" t="inlineStr">
-        <is>
-          <t>a:88.282</t>
-        </is>
-      </c>
-      <c r="I103" t="inlineStr"/>
-      <c r="J103" t="inlineStr"/>
-      <c r="K103" t="inlineStr"/>
-      <c r="L103" t="inlineStr"/>
-      <c r="M103" t="n">
-        <v>0</v>
-      </c>
-      <c r="N103" t="inlineStr">
-        <is>
-          <t>deck top, left  : 190 + 4,500 + 300 lap = 4,990  (8-243 (1)-1 N=110)</t>
+          <t>#   set    어느 벽에 붙을지. init 의 자세(rot)만 주면 방향 게이트가 벽을 고른다.</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>trebar</t>
-        </is>
-      </c>
-      <c r="B104" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C104" t="n">
-        <v>11</v>
-      </c>
-      <c r="D104" t="n">
-        <v>13</v>
-      </c>
-      <c r="E104" t="inlineStr"/>
-      <c r="F104" t="inlineStr">
-        <is>
-          <t>a:E2</t>
-        </is>
-      </c>
-      <c r="G104" t="inlineStr">
-        <is>
-          <t>a:7810,b:190</t>
-        </is>
-      </c>
-      <c r="H104" t="inlineStr">
-        <is>
-          <t>a:91.718</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
-      <c r="K104" t="inlineStr"/>
-      <c r="L104" t="inlineStr"/>
-      <c r="M104" t="n">
-        <v>0</v>
-      </c>
-      <c r="N104" t="inlineStr">
-        <is>
-          <t>deck top, right : 300 lap + 7,510 + 190 = 8,000  (8-243 (1) N=110)</t>
+          <t>#          set 은 벽을 고르는 것에 그치지 않고 철근을 그 벽으로 회전·이동시켜</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>trebar</t>
-        </is>
-      </c>
-      <c r="B105" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C105" t="n">
-        <v>11</v>
-      </c>
-      <c r="D105" t="n">
-        <v>13</v>
-      </c>
-      <c r="E105" t="inlineStr"/>
-      <c r="F105" t="inlineStr">
-        <is>
-          <t>b:E4</t>
-        </is>
-      </c>
-      <c r="G105" t="inlineStr">
-        <is>
-          <t>a:190,b:1400</t>
-        </is>
-      </c>
-      <c r="H105" t="inlineStr">
-        <is>
-          <t>a:88.282</t>
-        </is>
-      </c>
-      <c r="I105" t="inlineStr"/>
-      <c r="J105" t="inlineStr"/>
-      <c r="K105" t="inlineStr"/>
-      <c r="L105" t="inlineStr"/>
-      <c r="M105" t="n">
-        <v>0</v>
-      </c>
-      <c r="N105" t="inlineStr">
-        <is>
-          <t>right cantilever soffit at the tip = 1,590  (8-243 (2) N=110)</t>
+          <t>#          곧바로 SETTLED 로 만든다 — 사실상 답을 미리 넣어 주는 칸이었다.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t># trebar | 2-1 | 11 | 13 | | b:E13 | a:190,b:1400 | a:-91.718 | | | | | 0 | off: the left wall runs the other way. Needs growing against the wall direction</t>
+          <t>#   angs   꺾임각 88.282 / 91.718. 데크 -3% 에서 나온 유도값이고, 다리 방향은</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>#          고를 것이 아니라 정해져 있다 — 콘크리트 안쪽이다.</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t># --- 아직 안 넣은 것 (8-243 에 있다. 배치면을 정해야 한다) ---</t>
+          <t>#          Physics.keepEndsInsideConcrete 가 밖으로 향한 다리를 되돌린다.</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>#   (3)  H13 L=5,055 N=110      (4)  H13 L=5,035 N=110      (5) H13 L=4,000 N=110</t>
+          <t>#</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t>#   (6)-1~(6)-4  H22  A.v.r L=8,257  N=110   본체 6,763~7,710  + 다리 510 x 2</t>
+          <t># 아직 남은 것 :</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>#       -&gt; (6,763+7,710)/2 + 1,020 = 8,257 로 정확히 맞는다. **길이가 출력인 사례**</t>
+          <t>#   segs   조각 길이. 콘크리트까지 자라는 것이 아직 안 된다 — 기본값 400 에 머문다.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>#   (7)(7a) L=4,000  (8)(8a) L=3,090  (9)(9a) L=1,890/1,960  (10) H19 L=6,000</t>
+          <t>#          190   = 선단두께 280 - 2 x 피복 45  (유도값. 자동화 대상)</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>#   (11)(11-1)(12) H13  ㄷ자 500 x 150,  X = 206~480 / 212~486 (범위!)</t>
+          <t>#          4,800 / 7,810 = 겹이음 위치가 정하는 값 (설계 판단)</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>#   T2 H13 L=700 N=520 · T3 · D1 H16 · D2 H13 · D3 H16 · S2 H13</t>
+          <t>trebar</t>
+        </is>
+      </c>
+      <c r="B114" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="C114" t="n">
+        <v>11</v>
+      </c>
+      <c r="D114" t="n">
+        <v>13</v>
+      </c>
+      <c r="E114" t="inlineStr">
+        <is>
+          <t>-5000,100,-90</t>
+        </is>
+      </c>
+      <c r="F114" t="inlineStr"/>
+      <c r="G114" t="inlineStr">
+        <is>
+          <t>a:190,b:4800</t>
+        </is>
+      </c>
+      <c r="H114" t="inlineStr"/>
+      <c r="I114" t="inlineStr"/>
+      <c r="J114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
+      <c r="M114" t="n">
+        <v>0</v>
+      </c>
+      <c r="N114" t="inlineStr">
+        <is>
+          <t>deck top, left  : 190 + 4,500 + 300 lap = 4,990  (8-243 (1)-1 N=110)</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
+        <is>
+          <t>trebar</t>
+        </is>
+      </c>
+      <c r="B115" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C115" t="n">
+        <v>11</v>
+      </c>
+      <c r="D115" t="n">
+        <v>13</v>
+      </c>
+      <c r="E115" t="inlineStr">
+        <is>
+          <t>5000,-150,180</t>
+        </is>
+      </c>
+      <c r="F115" t="inlineStr"/>
+      <c r="G115" t="inlineStr">
+        <is>
+          <t>a:190,b:7810</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
+      <c r="M115" t="n">
+        <v>0</v>
+      </c>
+      <c r="N115" t="inlineStr">
+        <is>
+          <t>deck top, right : 190 + 7,510 + 300 lap = 8,000  (8-243 (1) N=110)</t>
+        </is>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>trebar</t>
+        </is>
+      </c>
+      <c r="B116" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C116" t="n">
+        <v>11</v>
+      </c>
+      <c r="D116" t="n">
+        <v>13</v>
+      </c>
+      <c r="E116" t="inlineStr">
+        <is>
+          <t>5800,-350,-90</t>
+        </is>
+      </c>
+      <c r="F116" t="inlineStr"/>
+      <c r="G116" t="inlineStr">
+        <is>
+          <t>a:190,b:1400</t>
+        </is>
+      </c>
+      <c r="H116" t="inlineStr"/>
+      <c r="I116" t="inlineStr"/>
+      <c r="J116" t="inlineStr"/>
+      <c r="K116" t="inlineStr"/>
+      <c r="L116" t="inlineStr"/>
+      <c r="M116" t="n">
+        <v>0</v>
+      </c>
+      <c r="N116" t="inlineStr">
+        <is>
+          <t>right cantilever soffit at the tip = 1,590  (8-243 (2) N=110)</t>
+        </is>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t># trebar | 2-1 | 11 | 13 | -5800,-350,90 | | a:190,b:1400 | | | | | | 0 | off: needs growing against the wall direction</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t># --- 아직 안 넣은 것 (8-243 에 있다. 배치면을 정해야 한다) ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>#   (3)  H13 L=5,055 N=110      (4)  H13 L=5,035 N=110      (5) H13 L=4,000 N=110</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>#   (6)-1~(6)-4  H22  A.v.r L=8,257  N=110   본체 6,763~7,710  + 다리 510 x 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>#       -&gt; (6,763+7,710)/2 + 1,020 = 8,257 로 정확히 맞는다. **길이가 출력인 사례**</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>#   (7)(7a) L=4,000  (8)(8a) L=3,090  (9)(9a) L=1,890/1,960  (10) H19 L=6,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>#   (11)(11-1)(12) H13  ㄷ자 500 x 150,  X = 206~480 / 212~486 (범위!)</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>#   T2 H13 L=700 N=520 · T3 · D1 H16 · D2 H13 · D3 H16 · S2 H13</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
         <is>
           <t>end</t>
         </is>

--- a/PSCBOX_S14.xlsx
+++ b/PSCBOX_S14.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N126"/>
+  <dimension ref="A1:N138"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2214,7 +2214,7 @@
     <row r="98">
       <c r="A98" t="inlineStr">
         <is>
-          <t># 8-243 SECTION A-A (= S14). 먼저 S15 에서 도는 것과 같은 꼴만 넣었다.</t>
+          <t># 8-243 SECTION A-A (= S14).</t>
         </is>
       </c>
     </row>
@@ -2228,292 +2228,516 @@
     <row r="100">
       <c r="A100" t="inlineStr">
         <is>
-          <t>#   code 11 = ㄱ자(A-&gt;B).  세그먼트는 **다리(190) 먼저**, 그 다음 몸통.</t>
+          <t>#</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="inlineStr">
         <is>
-          <t>#</t>
+          <t># 입력에서 뺀 것 — 엔진이 스스로 찾는다 :</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="inlineStr">
         <is>
-          <t># 입력에서 뺀 것 — 엔진이 스스로 찾는다 :</t>
+          <t>#   set    어느 벽에 붙을지. init 의 자세(rot)만 주면 방향 게이트가 벽을 고른다.</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="inlineStr">
         <is>
-          <t>#   set    어느 벽에 붙을지. init 의 자세(rot)만 주면 방향 게이트가 벽을 고른다.</t>
+          <t>#          set 은 벽을 고르는 것에 그치지 않고 철근을 그 벽으로 회전·이동시켜</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="inlineStr">
         <is>
-          <t>#          set 은 벽을 고르는 것에 그치지 않고 철근을 그 벽으로 회전·이동시켜</t>
+          <t>#          곧바로 SETTLED 로 만든다 — 사실상 답을 미리 넣어 주는 칸이었다.</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="inlineStr">
         <is>
-          <t>#          곧바로 SETTLED 로 만든다 — 사실상 답을 미리 넣어 주는 칸이었다.</t>
+          <t>#   angs   꺾임각 88.282 / 91.718 / 둔각 V 의 사이각. 전부 벽이 정하는 값이다.</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="inlineStr">
         <is>
-          <t>#   angs   꺾임각 88.282 / 91.718. 데크 -3% 에서 나온 유도값이고, 다리 방향은</t>
+          <t>#          조각이 제 벽에 안착한 뒤 두 직선의 교점으로 코너를 잇는다 — 각은 결과다.</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="inlineStr">
         <is>
-          <t>#          고를 것이 아니라 정해져 있다 — 콘크리트 안쪽이다.</t>
+          <t>#</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="inlineStr">
         <is>
-          <t>#          Physics.keepEndsInsideConcrete 가 밖으로 향한 다리를 되돌린다.</t>
+          <t># 방향 규칙 (rot 은 반시계가 + · bench/shape_rot.js 로 찍은 표) :</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>#   code 11  rot   0 → a 위   · b 오른쪽      rot  90 → a 왼쪽 · b 위</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="inlineStr">
         <is>
-          <t># 아직 남은 것 :</t>
+          <t>#            rot 180 → a 아래 · b 왼쪽        rot -90 → a 오른쪽 · b 아래</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="inlineStr">
         <is>
-          <t>#   segs   조각 길이. 콘크리트까지 자라는 것이 아직 안 된다 — 기본값 400 에 머문다.</t>
+          <t>#            a→b 는 언제나 시계방향 90 도. 거울상은 회전이 아니라 a·b 순서로 만든다.</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="inlineStr">
         <is>
-          <t>#          190   = 선단두께 280 - 2 x 피복 45  (유도값. 자동화 대상)</t>
+          <t>#   code 15  둔각 V. rot 0 → a 왼쪽 · b 오른쪽, 꺾임점이 아래, 두 법선 모두 아래.</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="inlineStr">
         <is>
-          <t>#          4,800 / 7,810 = 겹이음 위치가 정하는 값 (설계 판단)</t>
+          <t>#   code  1  직선. init 는 중점. rot 180 이면 법선이 아래를 본다.</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="inlineStr">
         <is>
-          <t>trebar</t>
-        </is>
-      </c>
-      <c r="B114" t="inlineStr">
-        <is>
-          <t>1-1</t>
-        </is>
-      </c>
-      <c r="C114" t="n">
-        <v>11</v>
-      </c>
-      <c r="D114" t="n">
-        <v>13</v>
-      </c>
-      <c r="E114" t="inlineStr">
-        <is>
-          <t>-5000,100,-90</t>
-        </is>
-      </c>
-      <c r="F114" t="inlineStr"/>
-      <c r="G114" t="inlineStr">
-        <is>
-          <t>a:190,b:4800</t>
-        </is>
-      </c>
-      <c r="H114" t="inlineStr"/>
-      <c r="I114" t="inlineStr"/>
-      <c r="J114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
-      <c r="L114" t="inlineStr"/>
-      <c r="M114" t="n">
-        <v>0</v>
-      </c>
-      <c r="N114" t="inlineStr">
-        <is>
-          <t>deck top, left  : 190 + 4,500 + 300 lap = 4,990  (8-243 (1)-1 N=110)</t>
+          <t>#</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="inlineStr">
         <is>
-          <t>trebar</t>
-        </is>
-      </c>
-      <c r="B115" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="C115" t="n">
-        <v>11</v>
-      </c>
-      <c r="D115" t="n">
-        <v>13</v>
-      </c>
-      <c r="E115" t="inlineStr">
-        <is>
-          <t>5000,-150,180</t>
-        </is>
-      </c>
-      <c r="F115" t="inlineStr"/>
-      <c r="G115" t="inlineStr">
-        <is>
-          <t>a:190,b:7810</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr"/>
-      <c r="I115" t="inlineStr"/>
-      <c r="J115" t="inlineStr"/>
-      <c r="K115" t="inlineStr"/>
-      <c r="L115" t="inlineStr"/>
-      <c r="M115" t="n">
-        <v>0</v>
-      </c>
-      <c r="N115" t="inlineStr">
-        <is>
-          <t>deck top, right : 190 + 7,510 + 300 lap = 8,000  (8-243 (1) N=110)</t>
+          <t># 아직 남은 것 :</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="inlineStr">
         <is>
-          <t>trebar</t>
-        </is>
-      </c>
-      <c r="B116" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="C116" t="n">
-        <v>11</v>
-      </c>
-      <c r="D116" t="n">
-        <v>13</v>
-      </c>
-      <c r="E116" t="inlineStr">
-        <is>
-          <t>5800,-350,-90</t>
-        </is>
-      </c>
-      <c r="F116" t="inlineStr"/>
-      <c r="G116" t="inlineStr">
-        <is>
-          <t>a:190,b:1400</t>
-        </is>
-      </c>
-      <c r="H116" t="inlineStr"/>
-      <c r="I116" t="inlineStr"/>
-      <c r="J116" t="inlineStr"/>
-      <c r="K116" t="inlineStr"/>
-      <c r="L116" t="inlineStr"/>
-      <c r="M116" t="n">
-        <v>0</v>
-      </c>
-      <c r="N116" t="inlineStr">
-        <is>
-          <t>right cantilever soffit at the tip = 1,590  (8-243 (2) N=110)</t>
+          <t>#   segs   조각 길이. 콘크리트까지 자라는 것이 아직 안 된다 — 도면 값을 넣는다.</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="inlineStr">
         <is>
-          <t># trebar | 2-1 | 11 | 13 | -5800,-350,90 | | a:190,b:1400 | | | | | | 0 | off: needs growing against the wall direction</t>
+          <t>#          190   = 선단두께 280 - 2 x 피복 45  (유도값. 자동화 대상)</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>#          4,800 / 7,810 = 겹이음 위치가 정하는 값 (설계 판단)</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="inlineStr">
         <is>
-          <t># --- 아직 안 넣은 것 (8-243 에 있다. 배치면을 정해야 한다) ---</t>
+          <t># --- 상부슬래브 상면 ---</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="inlineStr">
         <is>
-          <t>#   (3)  H13 L=5,055 N=110      (4)  H13 L=5,035 N=110      (5) H13 L=4,000 N=110</t>
+          <t>trebar</t>
+        </is>
+      </c>
+      <c r="B120" t="inlineStr">
+        <is>
+          <t>1-1</t>
+        </is>
+      </c>
+      <c r="C120" t="n">
+        <v>11</v>
+      </c>
+      <c r="D120" t="n">
+        <v>13</v>
+      </c>
+      <c r="E120" t="inlineStr">
+        <is>
+          <t>-6100,100,-90</t>
+        </is>
+      </c>
+      <c r="F120" t="inlineStr"/>
+      <c r="G120" t="inlineStr">
+        <is>
+          <t>a:4800,b:190</t>
+        </is>
+      </c>
+      <c r="H120" t="inlineStr"/>
+      <c r="I120" t="inlineStr"/>
+      <c r="J120" t="inlineStr"/>
+      <c r="K120" t="inlineStr"/>
+      <c r="L120" t="inlineStr"/>
+      <c r="M120" t="n">
+        <v>0</v>
+      </c>
+      <c r="N120" t="inlineStr">
+        <is>
+          <t>deck top, left  : 4,800 몸통 + 190 다리 = 4,990  (8-243 (1)-1 N=110)</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="inlineStr">
         <is>
-          <t>#   (6)-1~(6)-4  H22  A.v.r L=8,257  N=110   본체 6,763~7,710  + 다리 510 x 2</t>
+          <t>trebar</t>
+        </is>
+      </c>
+      <c r="B121" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="C121" t="n">
+        <v>11</v>
+      </c>
+      <c r="D121" t="n">
+        <v>13</v>
+      </c>
+      <c r="E121" t="inlineStr">
+        <is>
+          <t>5000,-150,180</t>
+        </is>
+      </c>
+      <c r="F121" t="inlineStr"/>
+      <c r="G121" t="inlineStr">
+        <is>
+          <t>a:190,b:7810</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr"/>
+      <c r="I121" t="inlineStr"/>
+      <c r="J121" t="inlineStr"/>
+      <c r="K121" t="inlineStr"/>
+      <c r="L121" t="inlineStr"/>
+      <c r="M121" t="n">
+        <v>0</v>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>deck top, right : 190 다리 + 7,810 몸통 = 8,000  (8-243 (1) N=110)</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="inlineStr">
         <is>
-          <t>#       -&gt; (6,763+7,710)/2 + 1,020 = 8,257 로 정확히 맞는다. **길이가 출력인 사례**</t>
+          <t># --- 캔틸레버 하단 (선단) ---</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="inlineStr">
         <is>
-          <t>#   (7)(7a) L=4,000  (8)(8a) L=3,090  (9)(9a) L=1,890/1,960  (10) H19 L=6,000</t>
+          <t>trebar</t>
+        </is>
+      </c>
+      <c r="B123" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="C123" t="n">
+        <v>11</v>
+      </c>
+      <c r="D123" t="n">
+        <v>13</v>
+      </c>
+      <c r="E123" t="inlineStr">
+        <is>
+          <t>6100,-400,90</t>
+        </is>
+      </c>
+      <c r="F123" t="inlineStr"/>
+      <c r="G123" t="inlineStr">
+        <is>
+          <t>a:1400,b:190</t>
+        </is>
+      </c>
+      <c r="H123" t="inlineStr"/>
+      <c r="I123" t="inlineStr"/>
+      <c r="J123" t="inlineStr"/>
+      <c r="K123" t="inlineStr"/>
+      <c r="L123" t="inlineStr"/>
+      <c r="M123" t="n">
+        <v>0</v>
+      </c>
+      <c r="N123" t="inlineStr">
+        <is>
+          <t>right cantilever soffit at the tip = 1,590  (8-243 (2) N=110)</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="inlineStr">
         <is>
-          <t>#   (11)(11-1)(12) H13  ㄷ자 500 x 150,  X = 206~480 / 212~486 (범위!)</t>
+          <t>trebar</t>
+        </is>
+      </c>
+      <c r="B124" t="inlineStr">
+        <is>
+          <t>2-1</t>
+        </is>
+      </c>
+      <c r="C124" t="n">
+        <v>11</v>
+      </c>
+      <c r="D124" t="n">
+        <v>13</v>
+      </c>
+      <c r="E124" t="inlineStr">
+        <is>
+          <t>-6100,-60,0</t>
+        </is>
+      </c>
+      <c r="F124" t="inlineStr"/>
+      <c r="G124" t="inlineStr">
+        <is>
+          <t>a:190,b:1400</t>
+        </is>
+      </c>
+      <c r="H124" t="inlineStr"/>
+      <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="L124" t="inlineStr"/>
+      <c r="M124" t="n">
+        <v>0</v>
+      </c>
+      <c r="N124" t="inlineStr">
+        <is>
+          <t>left  cantilever soffit at the tip = 1,590  (8-243 (2)-1 N=110)</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="inlineStr">
         <is>
-          <t>#   T2 H13 L=700 N=520 · T3 · D1 H16 · D2 H13 · D3 H16 · S2 H13</t>
+          <t># --- 상부슬래브 하단 + 캔틸레버 하단 (둔각 V. 꺾임점은 복부 위 낮은 자리) ---</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="inlineStr">
+        <is>
+          <t>#   도면은 이 셋을 한 줄로 그린다 : (4) 왼쪽 V | (5) 가운데 직선 | (3) 오른쪽 V</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>#   (3)(4) 의 2,540 다리는 헌치를 지나 평평한 구간까지 넘어간다 — 겹이음이다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>trebar</t>
+        </is>
+      </c>
+      <c r="B128" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C128" t="n">
+        <v>15</v>
+      </c>
+      <c r="D128" t="n">
+        <v>13</v>
+      </c>
+      <c r="E128" t="inlineStr">
+        <is>
+          <t>3250,-650,0</t>
+        </is>
+      </c>
+      <c r="F128" t="inlineStr"/>
+      <c r="G128" t="inlineStr">
+        <is>
+          <t>a:2540,b:2515</t>
+        </is>
+      </c>
+      <c r="H128" t="inlineStr"/>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
+      <c r="K128" t="inlineStr"/>
+      <c r="L128" t="inlineStr"/>
+      <c r="M128" t="n">
+        <v>0</v>
+      </c>
+      <c r="N128" t="inlineStr">
+        <is>
+          <t>right : 2,540 헌치쪽 + 2,515 캔틸레버쪽 = 5,055  (8-243 (3) N=110)</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>trebar</t>
+        </is>
+      </c>
+      <c r="B129" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C129" t="n">
+        <v>15</v>
+      </c>
+      <c r="D129" t="n">
+        <v>13</v>
+      </c>
+      <c r="E129" t="inlineStr">
+        <is>
+          <t>-3250,-460,0</t>
+        </is>
+      </c>
+      <c r="F129" t="inlineStr"/>
+      <c r="G129" t="inlineStr">
+        <is>
+          <t>a:2540,b:2515</t>
+        </is>
+      </c>
+      <c r="H129" t="inlineStr"/>
+      <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
+      <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr"/>
+      <c r="M129" t="n">
+        <v>0</v>
+      </c>
+      <c r="N129" t="inlineStr">
+        <is>
+          <t>left  : 2,540 캔틸레버쪽 + 2,515 헌치쪽 = 5,055  (8-243 (4) N=110)</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>trebar</t>
+        </is>
+      </c>
+      <c r="B130" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C130" t="n">
+        <v>1</v>
+      </c>
+      <c r="D130" t="n">
+        <v>13</v>
+      </c>
+      <c r="E130" t="inlineStr">
+        <is>
+          <t>0,-250,180</t>
+        </is>
+      </c>
+      <c r="F130" t="inlineStr"/>
+      <c r="G130" t="inlineStr">
+        <is>
+          <t>a:4000</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr"/>
+      <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
+      <c r="K130" t="inlineStr"/>
+      <c r="L130" t="inlineStr"/>
+      <c r="M130" t="n">
+        <v>0</v>
+      </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>top slab soffit across the centreline = 4,000  (8-243 (5) N=110)</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t># --- 아직 안 넣은 것 (8-243 에 있다. 배치면을 정해야 한다) ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>#   (6)-1~(6)-4  H22  A.v.r L=8,257  N=110   본체 6,763~7,710  + 다리 510 x 2</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>#       -&gt; (6,763+7,710)/2 + 1,020 = 8,257 로 정확히 맞는다. **길이가 출력인 사례**</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>#   (7)(7a) L=4,000  (8)(8a) L=3,090  (9)(9a) L=1,890/1,960  (10) H19 L=6,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>#   (11)(11-1)(12) H13  ㄷ자 500 x 150,  X = 206~480 / 212~486 (범위!)</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>#   T2 H13 L=700 N=520 · T3 · D1 H16 · D2 H13 · D3 H16 · S2 H13</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
         <is>
           <t>end</t>
         </is>

--- a/PSCBOX_S14.xlsx
+++ b/PSCBOX_S14.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N138"/>
+  <dimension ref="A1:N145"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2690,54 +2690,227 @@
     <row r="131">
       <c r="A131" t="inlineStr">
         <is>
-          <t>#</t>
+          <t># --- 복부철근 (ㄷ자. 몸통은 세로, 다리 둘은 콘크리트 안쪽으로) ---</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="inlineStr">
         <is>
-          <t># --- 아직 안 넣은 것 (8-243 에 있다. 배치면을 정해야 한다) ---</t>
+          <t>#   8-243 : (6)-1~(6)-4  H22  A.v.r L=8,257  N=110  본체 6,763~7,710 + 다리 510 x 2</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="inlineStr">
         <is>
-          <t>#   (6)-1~(6)-4  H22  A.v.r L=8,257  N=110   본체 6,763~7,710  + 다리 510 x 2</t>
+          <t>#   S14 에서는 본체가 TH 6,853 - 2 x 45 = 6,763 이다 — 범위의 아래끝과 정확히 같다.</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="inlineStr">
         <is>
-          <t>#       -&gt; (6,763+7,710)/2 + 1,020 = 8,257 로 정확히 맞는다. **길이가 출력인 사례**</t>
+          <t>#   **길이를 입력하지 않는다.** 조각 길이는 기본값에 둔다 — 벽이 정하게 한다.</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>#   (7)(7a) L=4,000  (8)(8a) L=3,090  (9)(9a) L=1,890/1,960  (10) H19 L=6,000</t>
+          <t>#   rot 은 다리가 콘크리트 안쪽을 보게 고른 것이다 (코드 21 · 90 은 다리 왼쪽 · -90 은 오른쪽)</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>#   (11)(11-1)(12) H13  ㄷ자 500 x 150,  X = 206~480 / 212~486 (범위!)</t>
+          <t>trebar</t>
+        </is>
+      </c>
+      <c r="B136" t="inlineStr">
+        <is>
+          <t>6-1</t>
+        </is>
+      </c>
+      <c r="C136" t="n">
+        <v>21</v>
+      </c>
+      <c r="D136" t="n">
+        <v>22</v>
+      </c>
+      <c r="E136" t="inlineStr">
+        <is>
+          <t>3450,-3530,90</t>
+        </is>
+      </c>
+      <c r="F136" t="inlineStr"/>
+      <c r="G136" t="inlineStr"/>
+      <c r="H136" t="inlineStr"/>
+      <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" t="n">
+        <v>0</v>
+      </c>
+      <c r="N136" t="inlineStr">
+        <is>
+          <t>right web, outer face  (8-243 (6)-1 N=110)</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="inlineStr">
         <is>
-          <t>#   T2 H13 L=700 N=520 · T3 · D1 H16 · D2 H13 · D3 H16 · S2 H13</t>
+          <t>trebar</t>
+        </is>
+      </c>
+      <c r="B137" t="inlineStr">
+        <is>
+          <t>6-2</t>
+        </is>
+      </c>
+      <c r="C137" t="n">
+        <v>21</v>
+      </c>
+      <c r="D137" t="n">
+        <v>22</v>
+      </c>
+      <c r="E137" t="inlineStr">
+        <is>
+          <t>3050,-3520,-90</t>
+        </is>
+      </c>
+      <c r="F137" t="inlineStr"/>
+      <c r="G137" t="inlineStr"/>
+      <c r="H137" t="inlineStr"/>
+      <c r="I137" t="inlineStr"/>
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr"/>
+      <c r="M137" t="n">
+        <v>0</v>
+      </c>
+      <c r="N137" t="inlineStr">
+        <is>
+          <t>right web, inner face  (8-243 (6)-2 N=110)</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="inlineStr">
+        <is>
+          <t>trebar</t>
+        </is>
+      </c>
+      <c r="B138" t="inlineStr">
+        <is>
+          <t>6-3</t>
+        </is>
+      </c>
+      <c r="C138" t="n">
+        <v>21</v>
+      </c>
+      <c r="D138" t="n">
+        <v>22</v>
+      </c>
+      <c r="E138" t="inlineStr">
+        <is>
+          <t>-3050,-3340,90</t>
+        </is>
+      </c>
+      <c r="F138" t="inlineStr"/>
+      <c r="G138" t="inlineStr"/>
+      <c r="H138" t="inlineStr"/>
+      <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="inlineStr"/>
+      <c r="L138" t="inlineStr"/>
+      <c r="M138" t="n">
+        <v>0</v>
+      </c>
+      <c r="N138" t="inlineStr">
+        <is>
+          <t>left  web, inner face  (8-243 (6)-3 N=110)</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>trebar</t>
+        </is>
+      </c>
+      <c r="B139" t="inlineStr">
+        <is>
+          <t>6-4</t>
+        </is>
+      </c>
+      <c r="C139" t="n">
+        <v>21</v>
+      </c>
+      <c r="D139" t="n">
+        <v>22</v>
+      </c>
+      <c r="E139" t="inlineStr">
+        <is>
+          <t>-3450,-3330,-90</t>
+        </is>
+      </c>
+      <c r="F139" t="inlineStr"/>
+      <c r="G139" t="inlineStr"/>
+      <c r="H139" t="inlineStr"/>
+      <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr"/>
+      <c r="M139" t="n">
+        <v>0</v>
+      </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>left  web, outer face  (8-243 (6)-4 N=110)</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t># --- 아직 안 넣은 것 (8-243 에 있다. 배치면을 정해야 한다) ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>#   (7)(7a) L=4,000  (8)(8a) L=3,090  (9)(9a) L=1,890/1,960  (10) H19 L=6,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>#   (11)(11-1)(12) H13  ㄷ자 500 x 150,  X = 206~480 / 212~486 (범위!)</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>#   T2 H13 L=700 N=520 · T3 · D1 H16 · D2 H13 · D3 H16 · S2 H13</t>
+        </is>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
         <is>
           <t>end</t>
         </is>

--- a/PSCBOX_S14.xlsx
+++ b/PSCBOX_S14.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N145"/>
+  <dimension ref="A1:N146"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2718,45 +2718,14 @@
     <row r="135">
       <c r="A135" t="inlineStr">
         <is>
-          <t>#   rot 은 다리가 콘크리트 안쪽을 보게 고른 것이다 (코드 21 · 90 은 다리 왼쪽 · -90 은 오른쪽)</t>
+          <t>#   ⑥-1 ⑥-4 는 코드 21(ㄷ) · ⑥-2 ⑥-3 은 코드 23(Z 크랭크) — 도면 상세가 그렇다.</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="inlineStr">
         <is>
-          <t>trebar</t>
-        </is>
-      </c>
-      <c r="B136" t="inlineStr">
-        <is>
-          <t>6-1</t>
-        </is>
-      </c>
-      <c r="C136" t="n">
-        <v>21</v>
-      </c>
-      <c r="D136" t="n">
-        <v>22</v>
-      </c>
-      <c r="E136" t="inlineStr">
-        <is>
-          <t>3450,-3530,90</t>
-        </is>
-      </c>
-      <c r="F136" t="inlineStr"/>
-      <c r="G136" t="inlineStr"/>
-      <c r="H136" t="inlineStr"/>
-      <c r="I136" t="inlineStr"/>
-      <c r="J136" t="inlineStr"/>
-      <c r="K136" t="inlineStr"/>
-      <c r="L136" t="inlineStr"/>
-      <c r="M136" t="n">
-        <v>0</v>
-      </c>
-      <c r="N136" t="inlineStr">
-        <is>
-          <t>right web, outer face  (8-243 (6)-1 N=110)</t>
+          <t>#   rot 은 다리가 콘크리트 안쪽을 보게 고른 것이다 (21 : 90 다리 왼쪽 · -90 오른쪽)</t>
         </is>
       </c>
     </row>
@@ -2768,7 +2737,7 @@
       </c>
       <c r="B137" t="inlineStr">
         <is>
-          <t>6-2</t>
+          <t>6-1</t>
         </is>
       </c>
       <c r="C137" t="n">
@@ -2779,7 +2748,7 @@
       </c>
       <c r="E137" t="inlineStr">
         <is>
-          <t>3050,-3520,-90</t>
+          <t>3450,-3530,90</t>
         </is>
       </c>
       <c r="F137" t="inlineStr"/>
@@ -2794,7 +2763,7 @@
       </c>
       <c r="N137" t="inlineStr">
         <is>
-          <t>right web, inner face  (8-243 (6)-2 N=110)</t>
+          <t>right web, outer face  (8-243 (6)-1 N=110)</t>
         </is>
       </c>
     </row>
@@ -2806,18 +2775,18 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>6-3</t>
+          <t>6-2</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D138" t="n">
         <v>22</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>-3050,-3340,90</t>
+          <t>3050,-3520,-90</t>
         </is>
       </c>
       <c r="F138" t="inlineStr"/>
@@ -2832,7 +2801,7 @@
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t>left  web, inner face  (8-243 (6)-3 N=110)</t>
+          <t>right web, inner face  (8-243 (6)-2 N=110)</t>
         </is>
       </c>
     </row>
@@ -2844,18 +2813,18 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>6-4</t>
+          <t>6-3</t>
         </is>
       </c>
       <c r="C139" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="D139" t="n">
         <v>22</v>
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>-3450,-3330,-90</t>
+          <t>-3050,-3340,90</t>
         </is>
       </c>
       <c r="F139" t="inlineStr"/>
@@ -2870,47 +2839,85 @@
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>left  web, outer face  (8-243 (6)-4 N=110)</t>
+          <t>left  web, inner face  (8-243 (6)-3 N=110)</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>trebar</t>
+        </is>
+      </c>
+      <c r="B140" t="inlineStr">
+        <is>
+          <t>6-4</t>
+        </is>
+      </c>
+      <c r="C140" t="n">
+        <v>21</v>
+      </c>
+      <c r="D140" t="n">
+        <v>22</v>
+      </c>
+      <c r="E140" t="inlineStr">
+        <is>
+          <t>-3450,-3330,-90</t>
+        </is>
+      </c>
+      <c r="F140" t="inlineStr"/>
+      <c r="G140" t="inlineStr"/>
+      <c r="H140" t="inlineStr"/>
+      <c r="I140" t="inlineStr"/>
+      <c r="J140" t="inlineStr"/>
+      <c r="K140" t="inlineStr"/>
+      <c r="L140" t="inlineStr"/>
+      <c r="M140" t="n">
+        <v>0</v>
+      </c>
+      <c r="N140" t="inlineStr">
+        <is>
+          <t>left  web, outer face  (8-243 (6)-4 N=110)</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="inlineStr">
         <is>
-          <t># --- 아직 안 넣은 것 (8-243 에 있다. 배치면을 정해야 한다) ---</t>
+          <t>#</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t>#   (7)(7a) L=4,000  (8)(8a) L=3,090  (9)(9a) L=1,890/1,960  (10) H19 L=6,000</t>
+          <t># --- 아직 안 넣은 것 (8-243 에 있다. 배치면을 정해야 한다) ---</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>#   (11)(11-1)(12) H13  ㄷ자 500 x 150,  X = 206~480 / 212~486 (범위!)</t>
+          <t>#   (7)(7a) L=4,000  (8)(8a) L=3,090  (9)(9a) L=1,890/1,960  (10) H19 L=6,000</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>#   T2 H13 L=700 N=520 · T3 · D1 H16 · D2 H13 · D3 H16 · S2 H13</t>
+          <t>#   (11)(11-1)(12) H13  ㄷ자 500 x 150,  X = 206~480 / 212~486 (범위!)</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
+        <is>
+          <t>#   T2 H13 L=700 N=520 · T3 · D1 H16 · D2 H13 · D3 H16 · S2 H13</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
         <is>
           <t>end</t>
         </is>

--- a/PSCBOX_S14.xlsx
+++ b/PSCBOX_S14.xlsx
@@ -2786,7 +2786,7 @@
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>3050,-3520,-90</t>
+          <t>3050,-3520,90</t>
         </is>
       </c>
       <c r="F138" t="inlineStr"/>

--- a/PSCBOX_S14.xlsx
+++ b/PSCBOX_S14.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N146"/>
+  <dimension ref="A1:N162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2775,18 +2775,18 @@
       </c>
       <c r="B138" t="inlineStr">
         <is>
-          <t>6-2</t>
+          <t>6-4</t>
         </is>
       </c>
       <c r="C138" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="D138" t="n">
         <v>22</v>
       </c>
       <c r="E138" t="inlineStr">
         <is>
-          <t>3050,-3520,90</t>
+          <t>-3450,-3330,-90</t>
         </is>
       </c>
       <c r="F138" t="inlineStr"/>
@@ -2801,7 +2801,7 @@
       </c>
       <c r="N138" t="inlineStr">
         <is>
-          <t>right web, inner face  (8-243 (6)-2 N=110)</t>
+          <t>left  web, outer face  (8-243 (6)-4 N=110)</t>
         </is>
       </c>
     </row>
@@ -2813,7 +2813,7 @@
       </c>
       <c r="B139" t="inlineStr">
         <is>
-          <t>6-3</t>
+          <t>6-2</t>
         </is>
       </c>
       <c r="C139" t="n">
@@ -2824,7 +2824,7 @@
       </c>
       <c r="E139" t="inlineStr">
         <is>
-          <t>-3050,-3340,90</t>
+          <t>3450,-3530,-90</t>
         </is>
       </c>
       <c r="F139" t="inlineStr"/>
@@ -2839,7 +2839,7 @@
       </c>
       <c r="N139" t="inlineStr">
         <is>
-          <t>left  web, inner face  (8-243 (6)-3 N=110)</t>
+          <t>right web, inner face  (8-243 (6)-2 N=110)</t>
         </is>
       </c>
     </row>
@@ -2851,18 +2851,20 @@
       </c>
       <c r="B140" t="inlineStr">
         <is>
-          <t>6-4</t>
-        </is>
-      </c>
-      <c r="C140" t="n">
-        <v>21</v>
+          <t>6-3</t>
+        </is>
+      </c>
+      <c r="C140" t="inlineStr">
+        <is>
+          <t>23-1</t>
+        </is>
       </c>
       <c r="D140" t="n">
         <v>22</v>
       </c>
       <c r="E140" t="inlineStr">
         <is>
-          <t>-3450,-3330,-90</t>
+          <t>-3050,-3340,90</t>
         </is>
       </c>
       <c r="F140" t="inlineStr"/>
@@ -2877,7 +2879,7 @@
       </c>
       <c r="N140" t="inlineStr">
         <is>
-          <t>left  web, outer face  (8-243 (6)-4 N=110)</t>
+          <t>left  web, inner face  (8-243 (6)-3 N=110)</t>
         </is>
       </c>
     </row>
@@ -2891,33 +2893,328 @@
     <row r="142">
       <c r="A142" t="inlineStr">
         <is>
-          <t># --- 아직 안 넣은 것 (8-243 에 있다. 배치면을 정해야 한다) ---</t>
+          <t># --- 하부슬래브 (8-243 의 형상상세에서 읽었다) ---</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="inlineStr">
         <is>
-          <t>#   (7)(7a) L=4,000  (8)(8a) L=3,090  (9)(9a) L=1,890/1,960  (10) H19 L=6,000</t>
+          <t>#   상면 : (8)-1 왼쪽 헌치 · (7) 가운데 · (8) 오른쪽 헌치   — 셋이 겹이음으로 이어진다</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="inlineStr">
         <is>
-          <t>#   (11)(11-1)(12) H13  ㄷ자 500 x 150,  X = 206~480 / 212~486 (범위!)</t>
+          <t>#   하면 : (9)-1 왼쪽 · (9) 오른쪽                        — 겹이음 380 (H19 는 450)</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="inlineStr">
         <is>
-          <t>#   T2 H13 L=700 N=520 · T3 · D1 H16 · D2 H13 · D3 H16 · S2 H13</t>
+          <t>#   H16 을 넣는다. 도면의 (7a)(8a)(9a) 는 같은 자리의 H19 로 번갈아 배근된다.</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="inlineStr">
+        <is>
+          <t>#   다리 380 · 300 과 몸통 길이는 겹이음이 정하는 값이라 도면 값을 그대로 넣는다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>#   rot 은 bench/shape_rot.js 의 표대로 골랐다 (코드 11 : rot 0 → a 코너 위 · b 오른쪽).</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>#   **거울상은 회전이 아니라 nors 로 만든다** — 다리가 코너 위이면서 몸통이 오른쪽인</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>#   꼴은 회전으로 안 나오고, 법선만 뒤집으면 된다 (nors a=-1,b=-1).</t>
+        </is>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>#   init 는 코드 11 의 기준점 = 코너다. 코너에서 콘크리트 안쪽으로 조금 넣어 둔다.</t>
+        </is>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>#   ⑧-1 ⑧ 의 다리는 복부 **내측**면(E17 · E22), ⑨-1 ⑨ 의 다리는 **외측**면(E10 · E7).</t>
+        </is>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>trebar</t>
+        </is>
+      </c>
+      <c r="B152" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C152" t="n">
+        <v>1</v>
+      </c>
+      <c r="D152" t="n">
+        <v>16</v>
+      </c>
+      <c r="E152" t="inlineStr">
+        <is>
+          <t>0,-6180,0</t>
+        </is>
+      </c>
+      <c r="F152" t="inlineStr"/>
+      <c r="G152" t="inlineStr">
+        <is>
+          <t>a:4000</t>
+        </is>
+      </c>
+      <c r="H152" t="inlineStr"/>
+      <c r="I152" t="inlineStr"/>
+      <c r="J152" t="inlineStr"/>
+      <c r="K152" t="inlineStr"/>
+      <c r="L152" t="inlineStr"/>
+      <c r="M152" t="n">
+        <v>0</v>
+      </c>
+      <c r="N152" t="inlineStr">
+        <is>
+          <t>bottom slab top, centre = 4,000  (8-243 (7) H16 N=55)</t>
+        </is>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>trebar</t>
+        </is>
+      </c>
+      <c r="B153" t="inlineStr">
+        <is>
+          <t>8-1</t>
+        </is>
+      </c>
+      <c r="C153" t="n">
+        <v>11</v>
+      </c>
+      <c r="D153" t="n">
+        <v>16</v>
+      </c>
+      <c r="E153" t="inlineStr">
+        <is>
+          <t>-3050,-5820,0</t>
+        </is>
+      </c>
+      <c r="F153" t="inlineStr"/>
+      <c r="G153" t="inlineStr">
+        <is>
+          <t>a:380,b:2615</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr"/>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>a=-1,b=-1</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr"/>
+      <c r="K153" t="inlineStr"/>
+      <c r="L153" t="inlineStr"/>
+      <c r="M153" t="n">
+        <v>0</v>
+      </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>bottom slab top, left  : 380 leg up the web + 2,615  (8-243 (8)-1 H16 L=3,105 N=55)</t>
+        </is>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>trebar</t>
+        </is>
+      </c>
+      <c r="B154" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C154" t="n">
+        <v>11</v>
+      </c>
+      <c r="D154" t="n">
+        <v>16</v>
+      </c>
+      <c r="E154" t="inlineStr">
+        <is>
+          <t>3050,-6000,90</t>
+        </is>
+      </c>
+      <c r="F154" t="inlineStr"/>
+      <c r="G154" t="inlineStr">
+        <is>
+          <t>a:2600,b:380</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr"/>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>a=-1,b=-1</t>
+        </is>
+      </c>
+      <c r="J154" t="inlineStr"/>
+      <c r="K154" t="inlineStr"/>
+      <c r="L154" t="inlineStr"/>
+      <c r="M154" t="n">
+        <v>0</v>
+      </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>bottom slab top, right : 2,600 + 380 leg up the web  (8-243 (8) H16 L=3,090 N=55)</t>
+        </is>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>trebar</t>
+        </is>
+      </c>
+      <c r="B155" t="inlineStr">
+        <is>
+          <t>9-1</t>
+        </is>
+      </c>
+      <c r="C155" t="n">
+        <v>11</v>
+      </c>
+      <c r="D155" t="n">
+        <v>16</v>
+      </c>
+      <c r="E155" t="inlineStr">
+        <is>
+          <t>-3450,-6700,0</t>
+        </is>
+      </c>
+      <c r="F155" t="inlineStr"/>
+      <c r="G155" t="inlineStr">
+        <is>
+          <t>a:300,b:1590</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr"/>
+      <c r="I155" t="inlineStr"/>
+      <c r="J155" t="inlineStr"/>
+      <c r="K155" t="inlineStr"/>
+      <c r="L155" t="inlineStr"/>
+      <c r="M155" t="n">
+        <v>0</v>
+      </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>bottom slab soffit, left  : 300 leg + 1,590  (8-243 (9)-1 H16 L=1,890 N=55)</t>
+        </is>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>trebar</t>
+        </is>
+      </c>
+      <c r="B156" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C156" t="n">
+        <v>11</v>
+      </c>
+      <c r="D156" t="n">
+        <v>16</v>
+      </c>
+      <c r="E156" t="inlineStr">
+        <is>
+          <t>3450,-6900,90</t>
+        </is>
+      </c>
+      <c r="F156" t="inlineStr"/>
+      <c r="G156" t="inlineStr">
+        <is>
+          <t>a:5320,b:300</t>
+        </is>
+      </c>
+      <c r="H156" t="inlineStr"/>
+      <c r="I156" t="inlineStr"/>
+      <c r="J156" t="inlineStr"/>
+      <c r="K156" t="inlineStr"/>
+      <c r="L156" t="inlineStr"/>
+      <c r="M156" t="n">
+        <v>0</v>
+      </c>
+      <c r="N156" t="inlineStr">
+        <is>
+          <t>bottom slab soffit, right : 5,320 + 300 leg  (8-243 (9) H16 L=6,000 N=55)</t>
+        </is>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>#</t>
+        </is>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t># --- 아직 안 넣은 것 (8-243 에 있다. 배치면을 정해야 한다) ---</t>
+        </is>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>#   (10) H19 L=6,000</t>
+        </is>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>#   (11)(11-1)(12) H13  ㄷ자 500 x 150,  X = 206~480 / 212~486 (범위!)</t>
+        </is>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>#   T2 H13 L=700 N=520 · T3 · D1 H16 · D2 H13 · D3 H16 · S2 H13</t>
+        </is>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
         <is>
           <t>end</t>
         </is>

--- a/PSCBOX_S14.xlsx
+++ b/PSCBOX_S14.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:N162"/>
+  <dimension ref="A1:N164"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -2935,116 +2935,42 @@
     <row r="148">
       <c r="A148" t="inlineStr">
         <is>
-          <t>#   **거울상은 회전이 아니라 nors 로 만든다** — 다리가 코너 위이면서 몸통이 오른쪽인</t>
+          <t>#   **안 적은 nors 는 기본값이다** — 뒤집어야 하는 것만 적는다.</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="inlineStr">
         <is>
-          <t>#   꼴은 회전으로 안 나오고, 법선만 뒤집으면 된다 (nors a=-1,b=-1).</t>
+          <t>#   다리(a)는 기본값 그대로 복부 **외측**면을 본다. 뒤집을 것은 몸통 하나뿐이다 :</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="inlineStr">
         <is>
-          <t>#   init 는 코드 11 의 기준점 = 코너다. 코너에서 콘크리트 안쪽으로 조금 넣어 둔다.</t>
+          <t>#     ⑧-1 은 rot 0 이라 몸통이 b → nors b=-1 · ⑧ 은 rot 90 이라 몸통이 a → nors a=-1</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="inlineStr">
         <is>
-          <t>#   ⑧-1 ⑧ 의 다리는 복부 **내측**면(E17 · E22), ⑨-1 ⑨ 의 다리는 **외측**면(E10 · E7).</t>
+          <t>#   (한때 양쪽을 다 뒤집어 a=-1,b=-1 로 적었더니 다리가 복부 **내측**면으로 붙었다.)</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="inlineStr">
         <is>
-          <t>trebar</t>
-        </is>
-      </c>
-      <c r="B152" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="C152" t="n">
-        <v>1</v>
-      </c>
-      <c r="D152" t="n">
-        <v>16</v>
-      </c>
-      <c r="E152" t="inlineStr">
-        <is>
-          <t>0,-6180,0</t>
-        </is>
-      </c>
-      <c r="F152" t="inlineStr"/>
-      <c r="G152" t="inlineStr">
-        <is>
-          <t>a:4000</t>
-        </is>
-      </c>
-      <c r="H152" t="inlineStr"/>
-      <c r="I152" t="inlineStr"/>
-      <c r="J152" t="inlineStr"/>
-      <c r="K152" t="inlineStr"/>
-      <c r="L152" t="inlineStr"/>
-      <c r="M152" t="n">
-        <v>0</v>
-      </c>
-      <c r="N152" t="inlineStr">
-        <is>
-          <t>bottom slab top, centre = 4,000  (8-243 (7) H16 N=55)</t>
+          <t>#   init 는 코드 11 의 기준점 = 코너다. 코너에서 콘크리트 안쪽으로 조금 넣어 둔다.</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="inlineStr">
         <is>
-          <t>trebar</t>
-        </is>
-      </c>
-      <c r="B153" t="inlineStr">
-        <is>
-          <t>8-1</t>
-        </is>
-      </c>
-      <c r="C153" t="n">
-        <v>11</v>
-      </c>
-      <c r="D153" t="n">
-        <v>16</v>
-      </c>
-      <c r="E153" t="inlineStr">
-        <is>
-          <t>-3050,-5820,0</t>
-        </is>
-      </c>
-      <c r="F153" t="inlineStr"/>
-      <c r="G153" t="inlineStr">
-        <is>
-          <t>a:380,b:2615</t>
-        </is>
-      </c>
-      <c r="H153" t="inlineStr"/>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>a=-1,b=-1</t>
-        </is>
-      </c>
-      <c r="J153" t="inlineStr"/>
-      <c r="K153" t="inlineStr"/>
-      <c r="L153" t="inlineStr"/>
-      <c r="M153" t="n">
-        <v>0</v>
-      </c>
-      <c r="N153" t="inlineStr">
-        <is>
-          <t>bottom slab top, left  : 380 leg up the web + 2,615  (8-243 (8)-1 H16 L=3,105 N=55)</t>
+          <t>#   ⑧-1 ⑧ ⑨-1 ⑨ 의 다리는 모두 복부 **외측**면 (E11 · E6 · E10 · E7).</t>
         </is>
       </c>
     </row>
@@ -3056,32 +2982,28 @@
       </c>
       <c r="B154" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C154" t="n">
-        <v>11</v>
+        <v>1</v>
       </c>
       <c r="D154" t="n">
         <v>16</v>
       </c>
       <c r="E154" t="inlineStr">
         <is>
-          <t>3050,-6000,90</t>
+          <t>0,-6180,0</t>
         </is>
       </c>
       <c r="F154" t="inlineStr"/>
       <c r="G154" t="inlineStr">
         <is>
-          <t>a:2600,b:380</t>
+          <t>a:4000</t>
         </is>
       </c>
       <c r="H154" t="inlineStr"/>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>a=-1,b=-1</t>
-        </is>
-      </c>
+      <c r="I154" t="inlineStr"/>
       <c r="J154" t="inlineStr"/>
       <c r="K154" t="inlineStr"/>
       <c r="L154" t="inlineStr"/>
@@ -3090,7 +3012,7 @@
       </c>
       <c r="N154" t="inlineStr">
         <is>
-          <t>bottom slab top, right : 2,600 + 380 leg up the web  (8-243 (8) H16 L=3,090 N=55)</t>
+          <t>bottom slab top, centre = 4,000  (8-243 (7) H16 N=55)</t>
         </is>
       </c>
     </row>
@@ -3102,7 +3024,7 @@
       </c>
       <c r="B155" t="inlineStr">
         <is>
-          <t>9-1</t>
+          <t>8-1</t>
         </is>
       </c>
       <c r="C155" t="n">
@@ -3113,17 +3035,21 @@
       </c>
       <c r="E155" t="inlineStr">
         <is>
-          <t>-3450,-6700,0</t>
+          <t>-3450,-5750,0</t>
         </is>
       </c>
       <c r="F155" t="inlineStr"/>
       <c r="G155" t="inlineStr">
         <is>
-          <t>a:300,b:1590</t>
+          <t>a:380,b:2615</t>
         </is>
       </c>
       <c r="H155" t="inlineStr"/>
-      <c r="I155" t="inlineStr"/>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>b=-1</t>
+        </is>
+      </c>
       <c r="J155" t="inlineStr"/>
       <c r="K155" t="inlineStr"/>
       <c r="L155" t="inlineStr"/>
@@ -3132,7 +3058,7 @@
       </c>
       <c r="N155" t="inlineStr">
         <is>
-          <t>bottom slab soffit, left  : 300 leg + 1,590  (8-243 (9)-1 H16 L=1,890 N=55)</t>
+          <t>bottom slab top, left  : 380 leg up the web outer face + 2,615  (8-243 (8)-1 H16 L=3,105 N=55)</t>
         </is>
       </c>
     </row>
@@ -3144,7 +3070,7 @@
       </c>
       <c r="B156" t="inlineStr">
         <is>
-          <t>9</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C156" t="n">
@@ -3155,17 +3081,21 @@
       </c>
       <c r="E156" t="inlineStr">
         <is>
-          <t>3450,-6900,90</t>
+          <t>3450,-5900,90</t>
         </is>
       </c>
       <c r="F156" t="inlineStr"/>
       <c r="G156" t="inlineStr">
         <is>
-          <t>a:5320,b:300</t>
+          <t>a:2600,b:380</t>
         </is>
       </c>
       <c r="H156" t="inlineStr"/>
-      <c r="I156" t="inlineStr"/>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>a=-1</t>
+        </is>
+      </c>
       <c r="J156" t="inlineStr"/>
       <c r="K156" t="inlineStr"/>
       <c r="L156" t="inlineStr"/>
@@ -3174,47 +3104,131 @@
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>bottom slab soffit, right : 5,320 + 300 leg  (8-243 (9) H16 L=6,000 N=55)</t>
+          <t>bottom slab top, right : 2,600 + 380 leg up the web outer face  (8-243 (8) H16 L=3,090 N=55)</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="inlineStr">
         <is>
-          <t>#</t>
+          <t>trebar</t>
+        </is>
+      </c>
+      <c r="B157" t="inlineStr">
+        <is>
+          <t>9-1</t>
+        </is>
+      </c>
+      <c r="C157" t="n">
+        <v>11</v>
+      </c>
+      <c r="D157" t="n">
+        <v>16</v>
+      </c>
+      <c r="E157" t="inlineStr">
+        <is>
+          <t>-3450,-6700,0</t>
+        </is>
+      </c>
+      <c r="F157" t="inlineStr"/>
+      <c r="G157" t="inlineStr">
+        <is>
+          <t>a:300,b:1590</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr"/>
+      <c r="I157" t="inlineStr"/>
+      <c r="J157" t="inlineStr"/>
+      <c r="K157" t="inlineStr"/>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" t="n">
+        <v>0</v>
+      </c>
+      <c r="N157" t="inlineStr">
+        <is>
+          <t>bottom slab soffit, left  : 300 leg + 1,590  (8-243 (9)-1 H16 L=1,890 N=55)</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="inlineStr">
         <is>
-          <t># --- 아직 안 넣은 것 (8-243 에 있다. 배치면을 정해야 한다) ---</t>
+          <t>trebar</t>
+        </is>
+      </c>
+      <c r="B158" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C158" t="n">
+        <v>11</v>
+      </c>
+      <c r="D158" t="n">
+        <v>16</v>
+      </c>
+      <c r="E158" t="inlineStr">
+        <is>
+          <t>3450,-6900,90</t>
+        </is>
+      </c>
+      <c r="F158" t="inlineStr"/>
+      <c r="G158" t="inlineStr">
+        <is>
+          <t>a:5320,b:300</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr"/>
+      <c r="I158" t="inlineStr"/>
+      <c r="J158" t="inlineStr"/>
+      <c r="K158" t="inlineStr"/>
+      <c r="L158" t="inlineStr"/>
+      <c r="M158" t="n">
+        <v>0</v>
+      </c>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>bottom slab soffit, right : 5,320 + 300 leg  (8-243 (9) H16 L=6,000 N=55)</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="inlineStr">
         <is>
-          <t>#   (10) H19 L=6,000</t>
+          <t>#</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="inlineStr">
         <is>
-          <t>#   (11)(11-1)(12) H13  ㄷ자 500 x 150,  X = 206~480 / 212~486 (범위!)</t>
+          <t># --- 아직 안 넣은 것 (8-243 에 있다. 배치면을 정해야 한다) ---</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="inlineStr">
         <is>
-          <t>#   T2 H13 L=700 N=520 · T3 · D1 H16 · D2 H13 · D3 H16 · S2 H13</t>
+          <t>#   (10) H19 L=6,000</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="inlineStr">
+        <is>
+          <t>#   (11)(11-1)(12) H13  ㄷ자 500 x 150,  X = 206~480 / 212~486 (범위!)</t>
+        </is>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>#   T2 H13 L=700 N=520 · T3 · D1 H16 · D2 H13 · D3 H16 · S2 H13</t>
+        </is>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
         <is>
           <t>end</t>
         </is>
